--- a/naver-place-crawler/results_hair/서구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/서구_미용실.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14557</v>
+        <v>14558</v>
       </c>
       <c r="Q5" t="n">
         <v>5887</v>
       </c>
       <c r="R5" t="n">
-        <v>20444</v>
+        <v>20445</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="Q8" t="n">
-        <v>5571</v>
+        <v>5573</v>
       </c>
       <c r="R8" t="n">
-        <v>8473</v>
+        <v>8476</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kangju_92@naver.com</t>
+          <t>forever62@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3975</v>
+        <v>3976</v>
       </c>
       <c r="Q24" t="n">
         <v>181</v>
       </c>
       <c r="R24" t="n">
-        <v>4156</v>
+        <v>4157</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>17267</v>
+        <v>17268</v>
       </c>
       <c r="Q26" t="n">
         <v>6858</v>
       </c>
       <c r="R26" t="n">
-        <v>24125</v>
+        <v>24126</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3824,10 +3824,10 @@
         <v>4044</v>
       </c>
       <c r="Q36" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="R36" t="n">
-        <v>4818</v>
+        <v>4819</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>minmin0319@naver.com</t>
+          <t>kuj0725@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5635</v>
+        <v>5639</v>
       </c>
       <c r="Q41" t="n">
         <v>1750</v>
       </c>
       <c r="R41" t="n">
-        <v>7385</v>
+        <v>7389</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4388,10 +4388,10 @@
         <v>6937</v>
       </c>
       <c r="Q42" t="n">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="R42" t="n">
-        <v>7961</v>
+        <v>7964</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5231,13 +5231,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>16012</v>
+        <v>16011</v>
       </c>
       <c r="Q51" t="n">
-        <v>6949</v>
+        <v>6951</v>
       </c>
       <c r="R51" t="n">
-        <v>22961</v>
+        <v>22962</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5422,10 +5422,10 @@
         <v>3446</v>
       </c>
       <c r="Q53" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="R53" t="n">
-        <v>7250</v>
+        <v>7251</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5892,10 +5892,10 @@
         <v>3159</v>
       </c>
       <c r="Q58" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="R58" t="n">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -5983,13 +5983,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="Q59" t="n">
         <v>88</v>
       </c>
       <c r="R59" t="n">
-        <v>2677</v>
+        <v>2679</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6550,10 +6550,10 @@
         <v>678</v>
       </c>
       <c r="Q65" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R65" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -6923,13 +6923,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="Q69" t="n">
         <v>145</v>
       </c>
       <c r="R69" t="n">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7397,13 +7397,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q74" t="n">
         <v>447</v>
       </c>
       <c r="R74" t="n">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -7678,10 +7678,10 @@
         <v>591</v>
       </c>
       <c r="Q77" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R77" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_hair/서구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/서구_미용실.xlsx
@@ -906,10 +906,10 @@
         <v>14558</v>
       </c>
       <c r="Q5" t="n">
-        <v>5887</v>
+        <v>5889</v>
       </c>
       <c r="R5" t="n">
-        <v>20445</v>
+        <v>20447</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
       </c>
       <c r="R6" t="n">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1131,11 +1131,7 @@
           <t>에이바헤어 청라커낼점</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dpdnjs3594@naver.com</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -1188,10 +1184,10 @@
         <v>2903</v>
       </c>
       <c r="Q8" t="n">
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="R8" t="n">
-        <v>8476</v>
+        <v>8477</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1470,10 +1466,10 @@
         <v>2224</v>
       </c>
       <c r="Q11" t="n">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="R11" t="n">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1752,10 +1748,10 @@
         <v>1695</v>
       </c>
       <c r="Q14" t="n">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="R14" t="n">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1981,11 +1977,7 @@
           <t>박승철헤어스투디오 검단신도시점</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>toomor@naver.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2357,11 +2349,7 @@
           <t>로이드밤 검단신도시점</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>forever62@naver.com</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2381,7 +2369,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2884,10 +2872,10 @@
         <v>17268</v>
       </c>
       <c r="Q26" t="n">
-        <v>6858</v>
+        <v>6860</v>
       </c>
       <c r="R26" t="n">
-        <v>24126</v>
+        <v>24128</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3203,11 +3191,7 @@
           <t>인히어센트 인천검단신도시점</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>km8189@naver.com</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3297,11 +3281,7 @@
           <t>모어무드헤어 검단신도시점</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>kk7711@naver.com</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3767,11 +3747,7 @@
           <t>자르시호 검단신도시점</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>winner3465@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -4009,13 +3985,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="Q38" t="n">
         <v>313</v>
       </c>
       <c r="R38" t="n">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4237,11 +4213,7 @@
           <t>에이그란데헤어 검단신도시점</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>kuj0725@naver.com</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -4385,13 +4357,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6937</v>
+        <v>6936</v>
       </c>
       <c r="Q42" t="n">
         <v>1027</v>
       </c>
       <c r="R42" t="n">
-        <v>7964</v>
+        <v>7963</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4479,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q43" t="n">
         <v>296</v>
       </c>
       <c r="R43" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4576,10 +4548,10 @@
         <v>752</v>
       </c>
       <c r="Q44" t="n">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="R44" t="n">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4613,11 +4585,7 @@
           <t>26도헤어 검단사거리역점</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>lhy8178@naver.com</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
@@ -4764,10 +4732,10 @@
         <v>1750</v>
       </c>
       <c r="Q46" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R46" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4895,11 +4863,7 @@
           <t>오드엠헤어 검단신도시점</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>oheunjung_@naver.com</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
@@ -4989,11 +4953,7 @@
           <t>26도헤어 신검단중앙역점</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>luludays_@naver.com</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
@@ -5043,13 +5003,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="Q49" t="n">
         <v>26</v>
       </c>
       <c r="R49" t="n">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5083,11 +5043,7 @@
           <t>온플릭 맨즈헤어 가정역점</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ttjjccrr@naver.com</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
@@ -5177,11 +5133,7 @@
           <t>아벨라움 인천청라점</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>sbk6751@naver.com</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5234,10 +5186,10 @@
         <v>16011</v>
       </c>
       <c r="Q51" t="n">
-        <v>6951</v>
+        <v>6958</v>
       </c>
       <c r="R51" t="n">
-        <v>22962</v>
+        <v>22969</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5422,10 +5374,10 @@
         <v>3446</v>
       </c>
       <c r="Q53" t="n">
-        <v>3805</v>
+        <v>3811</v>
       </c>
       <c r="R53" t="n">
-        <v>7251</v>
+        <v>7257</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5577,7 +5529,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5704,10 +5656,10 @@
         <v>1035</v>
       </c>
       <c r="Q56" t="n">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="R56" t="n">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5889,13 +5841,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="Q58" t="n">
         <v>216</v>
       </c>
       <c r="R58" t="n">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6141,7 +6093,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6329,7 +6281,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6644,10 +6596,10 @@
         <v>1011</v>
       </c>
       <c r="Q66" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R66" t="n">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6775,11 +6727,7 @@
           <t>26도헤어 청라점</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>beasj75@naver.com</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6923,13 +6871,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="Q69" t="n">
         <v>145</v>
       </c>
       <c r="R69" t="n">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7024,10 +6972,10 @@
         <v>3485</v>
       </c>
       <c r="Q70" t="n">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="R70" t="n">
-        <v>4728</v>
+        <v>4730</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7118,10 +7066,10 @@
         <v>2217</v>
       </c>
       <c r="Q71" t="n">
-        <v>7160</v>
+        <v>7164</v>
       </c>
       <c r="R71" t="n">
-        <v>9377</v>
+        <v>9381</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7212,10 +7160,10 @@
         <v>6836</v>
       </c>
       <c r="Q72" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R72" t="n">
-        <v>7353</v>
+        <v>7354</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7437,11 +7385,7 @@
           <t>레오바버샵 청라커넬웨이점</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>sienna_blossom@naver.com</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_hair/서구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/서구_미용실.xlsx
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5477</v>
+        <v>5479</v>
       </c>
       <c r="Q3" t="n">
         <v>104</v>
       </c>
       <c r="R3" t="n">
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4856</v>
+        <v>4858</v>
       </c>
       <c r="Q4" t="n">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="R4" t="n">
-        <v>5386</v>
+        <v>5387</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14558</v>
+        <v>14562</v>
       </c>
       <c r="Q5" t="n">
-        <v>5889</v>
+        <v>5894</v>
       </c>
       <c r="R5" t="n">
-        <v>20447</v>
+        <v>20456</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
       </c>
       <c r="R6" t="n">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1131,7 +1131,11 @@
           <t>에이바헤어 청라커낼점</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dpdnjs3594@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -1184,10 +1188,10 @@
         <v>2903</v>
       </c>
       <c r="Q8" t="n">
-        <v>5574</v>
+        <v>5585</v>
       </c>
       <c r="R8" t="n">
-        <v>8477</v>
+        <v>8488</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1278,10 +1282,10 @@
         <v>8735</v>
       </c>
       <c r="Q9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="R9" t="n">
-        <v>10148</v>
+        <v>10152</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1312,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>템드헤어룸 루원시티점</t>
+          <t>에이바헤어 검단사거리역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1288jh@naver.com</t>
+          <t>byong021369@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1444-1050</t>
+          <t>0507-1393-5888</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층 204호</t>
+          <t>인천광역시 서구 검단로 480 검단리치웰프라자 201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/temd_by.sooho</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1365,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1943</v>
+        <v>3200</v>
       </c>
       <c r="Q10" t="n">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="R10" t="n">
-        <v>2131</v>
+        <v>3256</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1262827062</t>
+          <t>1435550601</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262827062</t>
+          <t>https://m.place.naver.com/place/1435550601</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,44 +1410,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이철헤어커커 루원시티점</t>
+          <t>템드헤어룸 루원시티점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kerker2327@naver.com</t>
+          <t>1288jh@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1302-2326</t>
+          <t>0507-1444-1050</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 115 HB타워 2층 201호, 202호</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층 204호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://leechulhairkerker.co.kr/</t>
+          <t>https://www.instagram.com/temd_by.sooho</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1454,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2224</v>
+        <v>1943</v>
       </c>
       <c r="Q11" t="n">
-        <v>1229</v>
+        <v>188</v>
       </c>
       <c r="R11" t="n">
-        <v>3453</v>
+        <v>2131</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1976700186</t>
+          <t>1262827062</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976700186</t>
+          <t>https://m.place.naver.com/place/1262827062</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,39 +1504,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>이경민포레 검단신도시점</t>
+          <t>이철헤어커커 루원시티점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>foretgd@naver.com</t>
+          <t>kerker2327@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1323-6306</t>
+          <t>0507-1302-2326</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음1로 377 304, 305호</t>
+          <t>인천광역시 서구 봉오재3로 115 HB타워 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/foretgd</t>
+          <t>http://leechulhairkerker.co.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1548,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>857</v>
+        <v>2225</v>
       </c>
       <c r="Q12" t="n">
-        <v>2074</v>
+        <v>1230</v>
       </c>
       <c r="R12" t="n">
-        <v>2931</v>
+        <v>3455</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1818760676</t>
+          <t>1976700186</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1818760676</t>
+          <t>https://m.place.naver.com/place/1976700186</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1594,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>고정현헤어 청라2호점</t>
+          <t>이경민포레 검단신도시점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gohair7@naver.com</t>
+          <t>foretgd@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1316-3256</t>
+          <t>0507-1323-6306</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 16 키움프라자 2층</t>
+          <t>인천광역시 서구 이음1로 377 304, 305호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://www.gohair.co.kr</t>
+          <t>https://blog.naver.com/foretgd</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1651,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5843</v>
+        <v>857</v>
       </c>
       <c r="Q13" t="n">
-        <v>979</v>
+        <v>2075</v>
       </c>
       <c r="R13" t="n">
-        <v>6822</v>
+        <v>2932</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1607502409</t>
+          <t>1818760676</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1607502409</t>
+          <t>https://m.place.naver.com/place/1818760676</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1688,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>라라비긴헤어 가정점</t>
+          <t>고정현헤어 청라2호점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tjswhddlf961@naver.com</t>
+          <t>gohair7@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1492-6660</t>
+          <t>0507-1316-3256</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 16-1 203</t>
+          <t>인천광역시 서구 청라커낼로288번길 16 키움프라자 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/lalabegin_hyuna_</t>
+          <t>http://www.gohair.co.kr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1725,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1745,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1695</v>
+        <v>5841</v>
       </c>
       <c r="Q14" t="n">
-        <v>1453</v>
+        <v>979</v>
       </c>
       <c r="R14" t="n">
-        <v>3148</v>
+        <v>6820</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1447377305</t>
+          <t>1607502409</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447377305</t>
+          <t>https://m.place.naver.com/place/1607502409</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1782,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오도헤어 루원시티본점</t>
+          <t>라라비긴헤어 가정점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5do_hair@naver.com</t>
+          <t>tjswhddlf961@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1330-5983</t>
+          <t>0507-1492-6660</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미 루원센텀시티 2차 4층 415호, 416호</t>
+          <t>인천광역시 서구 염곡로498번안길 16-1 203</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5do_hair.b</t>
+          <t>http://www.instagram.com/lalabegin_hyuna_</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1839,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1258</v>
+        <v>1695</v>
       </c>
       <c r="Q15" t="n">
-        <v>65</v>
+        <v>1451</v>
       </c>
       <c r="R15" t="n">
-        <v>1323</v>
+        <v>3146</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,12 +1858,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1154757429</t>
+          <t>1447377305</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154757429</t>
+          <t>https://m.place.naver.com/place/1447377305</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1876,43 +1880,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>리안헤어 검단문화체육센터점</t>
+          <t>오도헤어 루원시티본점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>moon21131@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>akh@smartplug.kr</t>
-        </is>
-      </c>
+          <t>5do_hair@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1338-9105</t>
+          <t>0507-1330-5983</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 764 3층, 리안헤어</t>
+          <t>인천광역시 서구 가정로 451 벨라미 루원센텀시티 2차 4층 415호, 416호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/1566217</t>
+          <t>https://www.instagram.com/5do_hair.b</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>255</v>
+        <v>1258</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="R16" t="n">
-        <v>275</v>
+        <v>1323</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2096245961</t>
+          <t>1154757429</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096245961</t>
+          <t>https://m.place.naver.com/place/1154757429</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1974,35 +1974,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 검단신도시점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>리안헤어 검단문화체육센터점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>moon21131@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>akh@smartplug.kr</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1378-4671</t>
+          <t>0507-1338-9105</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 60 JS프라자 3층</t>
+          <t>인천광역시 서구 검단로 764 3층, 리안헤어</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/park_seung_chol_hair4671/</t>
+          <t>https://booking.naver.com/booking/13/bizes/1566217</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2027,13 +2035,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1384</v>
+        <v>255</v>
       </c>
       <c r="Q17" t="n">
-        <v>2172</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
-        <v>3556</v>
+        <v>275</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2050,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1484199591</t>
+          <t>2096245961</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1484199591</t>
+          <t>https://m.place.naver.com/place/2096245961</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2158,29 +2166,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>온어블 청라본점</t>
+          <t>박승철헤어스투디오 검단신도시점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nsscent@naver.com</t>
+          <t>toomor@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1371-5813</t>
+          <t>0507-1378-4671</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 A동 B1층 A19호 온어블헤어</t>
+          <t>인천광역시 서구 이음5로 60 JS프라자 3층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onable.official</t>
+          <t>https://www.instagram.com/park_seung_chol_hair4671/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2215,13 +2223,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1862</v>
+        <v>1384</v>
       </c>
       <c r="Q19" t="n">
-        <v>111</v>
+        <v>2172</v>
       </c>
       <c r="R19" t="n">
-        <v>1973</v>
+        <v>3556</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2238,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1088155978</t>
+          <t>1484199591</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088155978</t>
+          <t>https://m.place.naver.com/place/1484199591</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2349,7 +2357,11 @@
           <t>로이드밤 검단신도시점</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>kangju_92@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2496,10 +2508,10 @@
         <v>3411</v>
       </c>
       <c r="Q22" t="n">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="R22" t="n">
-        <v>4214</v>
+        <v>4215</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2872,10 +2884,10 @@
         <v>17268</v>
       </c>
       <c r="Q26" t="n">
-        <v>6860</v>
+        <v>6865</v>
       </c>
       <c r="R26" t="n">
-        <v>24128</v>
+        <v>24133</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2963,13 +2975,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="Q27" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R27" t="n">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3057,13 +3069,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4407</v>
+        <v>4408</v>
       </c>
       <c r="Q28" t="n">
         <v>1541</v>
       </c>
       <c r="R28" t="n">
-        <v>5948</v>
+        <v>5949</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3151,13 +3163,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="Q29" t="n">
         <v>26</v>
       </c>
       <c r="R29" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3191,7 +3203,11 @@
           <t>인히어센트 인천검단신도시점</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>km8189@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3281,7 +3297,11 @@
           <t>모어무드헤어 검단신도시점</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kk7711@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3428,10 +3448,10 @@
         <v>531</v>
       </c>
       <c r="Q32" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R32" t="n">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3710,10 +3730,10 @@
         <v>3300</v>
       </c>
       <c r="Q35" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="R35" t="n">
-        <v>4179</v>
+        <v>4177</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3747,7 +3767,11 @@
           <t>자르시호 검단신도시점</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>winner3465@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3797,13 +3821,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4044</v>
+        <v>4048</v>
       </c>
       <c r="Q36" t="n">
         <v>775</v>
       </c>
       <c r="R36" t="n">
-        <v>4819</v>
+        <v>4823</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3985,13 +4009,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="Q38" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R38" t="n">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4079,13 +4103,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="Q39" t="n">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="R39" t="n">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4176,10 +4200,10 @@
         <v>1540</v>
       </c>
       <c r="Q40" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="R40" t="n">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4213,7 +4237,11 @@
           <t>에이그란데헤어 검단신도시점</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kuj0725@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -4263,13 +4291,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="Q41" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="R41" t="n">
-        <v>7389</v>
+        <v>7391</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4357,13 +4385,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6936</v>
+        <v>6937</v>
       </c>
       <c r="Q42" t="n">
         <v>1027</v>
       </c>
       <c r="R42" t="n">
-        <v>7963</v>
+        <v>7964</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4585,7 +4613,11 @@
           <t>26도헤어 검단사거리역점</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>lhy8178@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
@@ -4638,10 +4670,10 @@
         <v>7752</v>
       </c>
       <c r="Q45" t="n">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="R45" t="n">
-        <v>8560</v>
+        <v>8558</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4732,10 +4764,10 @@
         <v>1750</v>
       </c>
       <c r="Q46" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R46" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4863,7 +4895,11 @@
           <t>오드엠헤어 검단신도시점</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>oheunjung_@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
@@ -4913,13 +4949,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="Q48" t="n">
         <v>95</v>
       </c>
       <c r="R48" t="n">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4953,7 +4989,11 @@
           <t>26도헤어 신검단중앙역점</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>luludays_@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
@@ -5043,7 +5083,11 @@
           <t>온플릭 맨즈헤어 가정역점</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ttjjccrr@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
@@ -5133,7 +5177,11 @@
           <t>아벨라움 인천청라점</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sbk6751@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -5183,13 +5231,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>16011</v>
+        <v>16015</v>
       </c>
       <c r="Q51" t="n">
-        <v>6958</v>
+        <v>6964</v>
       </c>
       <c r="R51" t="n">
-        <v>22969</v>
+        <v>22979</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5277,13 +5325,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>7798</v>
+        <v>7799</v>
       </c>
       <c r="Q52" t="n">
         <v>393</v>
       </c>
       <c r="R52" t="n">
-        <v>8191</v>
+        <v>8192</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5374,10 +5422,10 @@
         <v>3446</v>
       </c>
       <c r="Q53" t="n">
-        <v>3811</v>
+        <v>3818</v>
       </c>
       <c r="R53" t="n">
-        <v>7257</v>
+        <v>7264</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5562,10 +5610,10 @@
         <v>336</v>
       </c>
       <c r="Q55" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R55" t="n">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5656,10 +5704,10 @@
         <v>1035</v>
       </c>
       <c r="Q56" t="n">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="R56" t="n">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5750,10 +5798,10 @@
         <v>599</v>
       </c>
       <c r="Q57" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="R57" t="n">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5972,29 +6020,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>틔움헤어 검단신도시점</t>
+          <t>온플릭 맨즈헤어 루원시티점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jhhsk1k2@naver.com</t>
+          <t>onfleek_manshair@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>070-4107-9750</t>
+          <t>0507-1493-5507</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서로3로 198 202호</t>
+          <t>인천광역시 서구 가정로 406 루원지웰시티푸르지오 상가 A동 305</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/t.um_hair/</t>
+          <t>https://www.instagram.com/onfleekmans1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6029,13 +6077,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1037</v>
+        <v>1938</v>
       </c>
       <c r="Q60" t="n">
-        <v>2231</v>
+        <v>315</v>
       </c>
       <c r="R60" t="n">
-        <v>3268</v>
+        <v>2253</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,12 +6092,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1624914423</t>
+          <t>1484529672</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1624914423</t>
+          <t>https://m.place.naver.com/place/1484529672</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6066,29 +6114,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>카이정헤어 인천청라점</t>
+          <t>틔움헤어 검단신도시점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kaijung11@naver.com</t>
+          <t>jhhsk1k2@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1481-0151</t>
+          <t>070-4107-9750</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 2층 210호</t>
+          <t>인천광역시 서구 서로3로 198 202호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCZURnxox0laAqOaNmA9KJYg</t>
+          <t>https://www.instagram.com/t.um_hair/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,13 +6171,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>8172</v>
+        <v>1037</v>
       </c>
       <c r="Q61" t="n">
-        <v>832</v>
+        <v>2231</v>
       </c>
       <c r="R61" t="n">
-        <v>9004</v>
+        <v>3268</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,12 +6186,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1761969092</t>
+          <t>1624914423</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1761969092</t>
+          <t>https://m.place.naver.com/place/1624914423</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6160,29 +6208,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오르빗헤어</t>
+          <t>카이정헤어 인천청라점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kanghj0426@naver.com</t>
+          <t>kaijung11@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1374-5207</t>
+          <t>0507-1481-0151</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 468 102호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 2층 210호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orbit__hair</t>
+          <t>https://youtube.com/channel/UCZURnxox0laAqOaNmA9KJYg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6217,13 +6265,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>142</v>
+        <v>8174</v>
       </c>
       <c r="Q62" t="n">
-        <v>46</v>
+        <v>832</v>
       </c>
       <c r="R62" t="n">
-        <v>188</v>
+        <v>9006</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,12 +6280,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2037381163</t>
+          <t>1761969092</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037381163</t>
+          <t>https://m.place.naver.com/place/1761969092</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6254,29 +6302,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>로이드밤 검단사거리역점</t>
+          <t>오르빗헤어</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jamjam5257@naver.com</t>
+          <t>kanghj0426@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-561-8233</t>
+          <t>0507-1374-5207</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 474 뷰비스타운 2층 로이드밤헤어</t>
+          <t>인천광역시 서구 염곡로 468 102호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.lloydbomb.com/</t>
+          <t>https://www.instagram.com/orbit__hair</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6291,7 +6339,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6302,7 +6350,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6311,13 +6359,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2843</v>
+        <v>142</v>
       </c>
       <c r="Q63" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="R63" t="n">
-        <v>2918</v>
+        <v>188</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,12 +6374,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>521195559</t>
+          <t>2037381163</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/521195559</t>
+          <t>https://m.place.naver.com/place/2037381163</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6348,29 +6396,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>디아토 헤어 검단신도시점</t>
+          <t>로이드밤 검단사거리역점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>boung7@naver.com</t>
+          <t>jamjam5257@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1346-9154</t>
+          <t>032-561-8233</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 62 정인프라자 702호 디아토 헤어</t>
+          <t>인천광역시 서구 검단로 474 뷰비스타운 2층 로이드밤헤어</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/d.atto_hm?igsh=N2FkMGplamoyaG9w</t>
+          <t>http://www.lloydbomb.com/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6385,7 +6433,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6396,7 +6444,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6405,13 +6453,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>745</v>
+        <v>2843</v>
       </c>
       <c r="Q64" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="R64" t="n">
-        <v>848</v>
+        <v>2918</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,12 +6468,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1254089300</t>
+          <t>521195559</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1254089300</t>
+          <t>https://m.place.naver.com/place/521195559</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6442,29 +6490,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에이엔센트 청라점</t>
+          <t>디아토 헤어 검단신도시점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sosg4854@naver.com</t>
+          <t>boung7@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1350-7019</t>
+          <t>0507-1346-9154</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 상가 102동 234호</t>
+          <t>인천광역시 서구 이음5로 62 정인프라자 702호 디아토 헤어</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://www.youtube.com/@김가빈-m6d2j</t>
+          <t>https://www.instagram.com/d.atto_hm?igsh=N2FkMGplamoyaG9w</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6499,13 +6547,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>678</v>
+        <v>745</v>
       </c>
       <c r="Q65" t="n">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="R65" t="n">
-        <v>868</v>
+        <v>848</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,12 +6562,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1285080360</t>
+          <t>1254089300</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285080360</t>
+          <t>https://m.place.naver.com/place/1254089300</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6593,13 +6641,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q66" t="n">
         <v>278</v>
       </c>
       <c r="R66" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6687,13 +6735,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3602</v>
+        <v>3603</v>
       </c>
       <c r="Q67" t="n">
         <v>704</v>
       </c>
       <c r="R67" t="n">
-        <v>4306</v>
+        <v>4307</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6780,10 +6828,10 @@
         <v>5542</v>
       </c>
       <c r="Q68" t="n">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R68" t="n">
-        <v>6394</v>
+        <v>6393</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -7066,10 +7114,10 @@
         <v>2217</v>
       </c>
       <c r="Q71" t="n">
-        <v>7164</v>
+        <v>7176</v>
       </c>
       <c r="R71" t="n">
-        <v>9381</v>
+        <v>9393</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7157,13 +7205,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>6836</v>
+        <v>6837</v>
       </c>
       <c r="Q72" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R72" t="n">
-        <v>7354</v>
+        <v>7357</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7385,7 +7433,11 @@
           <t>레오바버샵 청라커넬웨이점</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sienna_blossom@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
